--- a/artfynd/A 21960-2024 artfynd.xlsx
+++ b/artfynd/A 21960-2024 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117890037</v>
+        <v>117889018</v>
       </c>
       <c r="B4" t="n">
-        <v>97836</v>
+        <v>57303</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,38 +911,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sparvatorpet (Sparvatorpet), Ög</t>
+          <t>Sparvatorpet (Ingabola), Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>484519</v>
+        <v>484421</v>
       </c>
       <c r="R4" t="n">
-        <v>6452938</v>
+        <v>6452892</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -974,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117889018</v>
+        <v>117890037</v>
       </c>
       <c r="B5" t="n">
-        <v>57303</v>
+        <v>97836</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,43 +1028,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sparvatorpet (Ingabola), Ög</t>
+          <t>Sparvatorpet (Sparvatorpet), Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>484421</v>
+        <v>484519</v>
       </c>
       <c r="R5" t="n">
-        <v>6452892</v>
+        <v>6452938</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 21960-2024 artfynd.xlsx
+++ b/artfynd/A 21960-2024 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117888959</v>
+        <v>117890037</v>
       </c>
       <c r="B3" t="n">
         <v>97836</v>
@@ -823,14 +823,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hällemon (Hällemon), Ög</t>
+          <t>Sparvatorpet (Sparvatorpet), Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>484406</v>
+        <v>484519</v>
       </c>
       <c r="R3" t="n">
-        <v>6452861</v>
+        <v>6452938</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117889018</v>
+        <v>117888959</v>
       </c>
       <c r="B4" t="n">
-        <v>57303</v>
+        <v>97836</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,43 +911,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sparvatorpet (Ingabola), Ög</t>
+          <t>Hällemon (Hällemon), Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>484421</v>
+        <v>484406</v>
       </c>
       <c r="R4" t="n">
-        <v>6452892</v>
+        <v>6452861</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -979,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117890037</v>
+        <v>117889018</v>
       </c>
       <c r="B5" t="n">
-        <v>97836</v>
+        <v>57303</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,38 +1023,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sparvatorpet (Sparvatorpet), Ög</t>
+          <t>Sparvatorpet (Ingabola), Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>484519</v>
+        <v>484421</v>
       </c>
       <c r="R5" t="n">
-        <v>6452938</v>
+        <v>6452892</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117908415</v>
+        <v>117908201</v>
       </c>
       <c r="B7" t="n">
-        <v>96791</v>
+        <v>97836</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,25 +1247,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,14 +1275,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hällemon7, Ög</t>
+          <t>Hällemon5, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>484302</v>
+        <v>484459</v>
       </c>
       <c r="R7" t="n">
-        <v>6452746</v>
+        <v>6452931</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1323,6 +1323,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1341,7 +1342,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117908207</v>
+        <v>117908199</v>
       </c>
       <c r="B8" t="n">
         <v>97836</v>
@@ -1381,14 +1382,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hällemon6, Ög</t>
+          <t>Hällemon4, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>484463</v>
+        <v>484464</v>
       </c>
       <c r="R8" t="n">
-        <v>6452943</v>
+        <v>6452935</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1448,10 +1449,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117908201</v>
+        <v>117908415</v>
       </c>
       <c r="B9" t="n">
-        <v>97836</v>
+        <v>96791</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1460,25 +1461,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1488,14 +1489,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hällemon5, Ög</t>
+          <t>Hällemon7, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>484459</v>
+        <v>484302</v>
       </c>
       <c r="R9" t="n">
-        <v>6452931</v>
+        <v>6452746</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1536,7 +1537,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1555,7 +1555,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117908175</v>
+        <v>117908151</v>
       </c>
       <c r="B10" t="n">
         <v>97836</v>
@@ -1595,14 +1595,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hällemon2, Ög</t>
+          <t>Hällemon1, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>484410</v>
+        <v>484411</v>
       </c>
       <c r="R10" t="n">
-        <v>6452852</v>
+        <v>6452845</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1655,14 +1655,14 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jonas Lindebring, Carina Faxén, Malin Gröndahl Maass</t>
+          <t>Jonas Lindebring, Carina Faxén</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117908151</v>
+        <v>117908190</v>
       </c>
       <c r="B11" t="n">
         <v>97836</v>
@@ -1702,14 +1702,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hällemon1, Ög</t>
+          <t>Hällemon3, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>484411</v>
+        <v>484463</v>
       </c>
       <c r="R11" t="n">
-        <v>6452845</v>
+        <v>6452931</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1762,14 +1762,14 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jonas Lindebring, Carina Faxén</t>
+          <t>Jonas Lindebring, Carina Faxén, Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117908190</v>
+        <v>117908207</v>
       </c>
       <c r="B12" t="n">
         <v>97836</v>
@@ -1809,14 +1809,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hällemon3, Ög</t>
+          <t>Hällemon6, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
         <v>484463</v>
       </c>
       <c r="R12" t="n">
-        <v>6452931</v>
+        <v>6452943</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1876,7 +1876,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117908199</v>
+        <v>117908175</v>
       </c>
       <c r="B13" t="n">
         <v>97836</v>
@@ -1916,14 +1916,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hällemon4, Ög</t>
+          <t>Hällemon2, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>484464</v>
+        <v>484410</v>
       </c>
       <c r="R13" t="n">
-        <v>6452935</v>
+        <v>6452852</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>

--- a/artfynd/A 21960-2024 artfynd.xlsx
+++ b/artfynd/A 21960-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117889700</v>
+        <v>117888959</v>
       </c>
       <c r="B2" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>484454</v>
+        <v>484406</v>
       </c>
       <c r="R2" t="n">
-        <v>6452948</v>
+        <v>6452861</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117890037</v>
+        <v>117889018</v>
       </c>
       <c r="B3" t="n">
-        <v>97836</v>
+        <v>57304</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,38 +799,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sparvatorpet (Sparvatorpet), Ög</t>
+          <t>Sparvatorpet (Ingabola), Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>484519</v>
+        <v>484421</v>
       </c>
       <c r="R3" t="n">
-        <v>6452938</v>
+        <v>6452892</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117888959</v>
+        <v>117889700</v>
       </c>
       <c r="B4" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>484406</v>
+        <v>484454</v>
       </c>
       <c r="R4" t="n">
-        <v>6452861</v>
+        <v>6452948</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -974,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117889018</v>
+        <v>117890037</v>
       </c>
       <c r="B5" t="n">
-        <v>57303</v>
+        <v>97838</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,43 +1028,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sparvatorpet (Ingabola), Ög</t>
+          <t>Sparvatorpet (Sparvatorpet), Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>484421</v>
+        <v>484519</v>
       </c>
       <c r="R5" t="n">
-        <v>6452892</v>
+        <v>6452938</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117908451</v>
+        <v>117908207</v>
       </c>
       <c r="B6" t="n">
-        <v>5480</v>
+        <v>97838</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,43 +1140,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>101410</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hällemon8, Ög</t>
+          <t>Hällemon6, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>484343</v>
+        <v>484463</v>
       </c>
       <c r="R6" t="n">
-        <v>6452808</v>
+        <v>6452943</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1217,6 +1216,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117908201</v>
+        <v>117908175</v>
       </c>
       <c r="B7" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,14 +1275,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hällemon5, Ög</t>
+          <t>Hällemon2, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>484459</v>
+        <v>484410</v>
       </c>
       <c r="R7" t="n">
-        <v>6452931</v>
+        <v>6452852</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1342,10 +1342,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117908199</v>
+        <v>117908190</v>
       </c>
       <c r="B8" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,14 +1382,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hällemon4, Ög</t>
+          <t>Hällemon3, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>484464</v>
+        <v>484463</v>
       </c>
       <c r="R8" t="n">
-        <v>6452935</v>
+        <v>6452931</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1449,10 +1449,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117908415</v>
+        <v>117908201</v>
       </c>
       <c r="B9" t="n">
-        <v>96791</v>
+        <v>97838</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1461,25 +1461,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1489,14 +1489,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hällemon7, Ög</t>
+          <t>Hällemon5, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>484302</v>
+        <v>484459</v>
       </c>
       <c r="R9" t="n">
-        <v>6452746</v>
+        <v>6452931</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1537,6 +1537,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1555,10 +1556,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117908151</v>
+        <v>117908415</v>
       </c>
       <c r="B10" t="n">
-        <v>97836</v>
+        <v>96793</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1567,25 +1568,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1595,14 +1596,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hällemon1, Ög</t>
+          <t>Hällemon7, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>484411</v>
+        <v>484302</v>
       </c>
       <c r="R10" t="n">
-        <v>6452845</v>
+        <v>6452746</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1643,7 +1644,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1655,17 +1655,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jonas Lindebring, Carina Faxén</t>
+          <t>Jonas Lindebring, Carina Faxén, Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117908190</v>
+        <v>117908151</v>
       </c>
       <c r="B11" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1702,14 +1702,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hällemon3, Ög</t>
+          <t>Hällemon1, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>484463</v>
+        <v>484411</v>
       </c>
       <c r="R11" t="n">
-        <v>6452931</v>
+        <v>6452845</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1762,17 +1762,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jonas Lindebring, Carina Faxén, Malin Gröndahl Maass</t>
+          <t>Jonas Lindebring, Carina Faxén</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117908207</v>
+        <v>117908199</v>
       </c>
       <c r="B12" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1809,14 +1809,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hällemon6, Ög</t>
+          <t>Hällemon4, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>484463</v>
+        <v>484464</v>
       </c>
       <c r="R12" t="n">
-        <v>6452943</v>
+        <v>6452935</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1876,10 +1876,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117908175</v>
+        <v>117908451</v>
       </c>
       <c r="B13" t="n">
-        <v>97836</v>
+        <v>5480</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1888,42 +1888,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>101410</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hällemon2, Ög</t>
+          <t>Hällemon8, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>484410</v>
+        <v>484343</v>
       </c>
       <c r="R13" t="n">
-        <v>6452852</v>
+        <v>6452808</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1964,7 +1965,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 21960-2024 artfynd.xlsx
+++ b/artfynd/A 21960-2024 artfynd.xlsx
@@ -1986,7 +1986,7 @@
         <v>121264388</v>
       </c>
       <c r="B14" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         <v>121264390</v>
       </c>
       <c r="B15" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 21960-2024 artfynd.xlsx
+++ b/artfynd/A 21960-2024 artfynd.xlsx
@@ -1986,7 +1986,7 @@
         <v>121264388</v>
       </c>
       <c r="B14" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         <v>121264390</v>
       </c>
       <c r="B15" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 21960-2024 artfynd.xlsx
+++ b/artfynd/A 21960-2024 artfynd.xlsx
@@ -1983,10 +1983,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121264388</v>
+        <v>121264390</v>
       </c>
       <c r="B14" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2019,17 +2019,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hällemon NO 700 m, Ög</t>
+          <t>Hällemon NO 600 m, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>484461</v>
+        <v>484410</v>
       </c>
       <c r="R14" t="n">
-        <v>6452943</v>
+        <v>6452856</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>E-Öde-0339</t>
+          <t>E-Öde-0337</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>O484463, N6452943 (±5m)</t>
+          <t>O484410, N6452852 (±5m)</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jonas Lindebring</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2099,10 +2099,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121264390</v>
+        <v>121264388</v>
       </c>
       <c r="B15" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2135,17 +2135,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hällemon NO 600 m, Ög</t>
+          <t>Hällemon NO 700 m, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>484410</v>
+        <v>484461</v>
       </c>
       <c r="R15" t="n">
-        <v>6452856</v>
+        <v>6452943</v>
       </c>
       <c r="S15" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>E-Öde-0337</t>
+          <t>E-Öde-0339</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>O484410, N6452852 (±5m)</t>
+          <t>O484463, N6452943 (±5m)</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Jonas Lindebring</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">

--- a/artfynd/A 21960-2024 artfynd.xlsx
+++ b/artfynd/A 21960-2024 artfynd.xlsx
@@ -1983,10 +1983,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121264390</v>
+        <v>121264388</v>
       </c>
       <c r="B14" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2019,17 +2019,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hällemon NO 600 m, Ög</t>
+          <t>Hällemon NO 700 m, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>484410</v>
+        <v>484461</v>
       </c>
       <c r="R14" t="n">
-        <v>6452856</v>
+        <v>6452943</v>
       </c>
       <c r="S14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>E-Öde-0337</t>
+          <t>E-Öde-0339</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>O484410, N6452852 (±5m)</t>
+          <t>O484463, N6452943 (±5m)</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Jonas Lindebring</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2099,10 +2099,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121264388</v>
+        <v>121264390</v>
       </c>
       <c r="B15" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2135,17 +2135,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hällemon NO 700 m, Ög</t>
+          <t>Hällemon NO 600 m, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>484461</v>
+        <v>484410</v>
       </c>
       <c r="R15" t="n">
-        <v>6452943</v>
+        <v>6452856</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>E-Öde-0339</t>
+          <t>E-Öde-0337</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>O484463, N6452943 (±5m)</t>
+          <t>O484410, N6452852 (±5m)</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jonas Lindebring</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">

--- a/artfynd/A 21960-2024 artfynd.xlsx
+++ b/artfynd/A 21960-2024 artfynd.xlsx
@@ -1983,7 +1983,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121264388</v>
+        <v>121264390</v>
       </c>
       <c r="B14" t="n">
         <v>98098</v>
@@ -2019,17 +2019,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hällemon NO 700 m, Ög</t>
+          <t>Hällemon NO 600 m, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>484461</v>
+        <v>484410</v>
       </c>
       <c r="R14" t="n">
-        <v>6452943</v>
+        <v>6452856</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>E-Öde-0339</t>
+          <t>E-Öde-0337</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>O484463, N6452943 (±5m)</t>
+          <t>O484410, N6452852 (±5m)</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jonas Lindebring</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2099,7 +2099,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121264390</v>
+        <v>121264388</v>
       </c>
       <c r="B15" t="n">
         <v>98098</v>
@@ -2135,17 +2135,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hällemon NO 600 m, Ög</t>
+          <t>Hällemon NO 700 m, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>484410</v>
+        <v>484461</v>
       </c>
       <c r="R15" t="n">
-        <v>6452856</v>
+        <v>6452943</v>
       </c>
       <c r="S15" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>E-Öde-0337</t>
+          <t>E-Öde-0339</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>O484410, N6452852 (±5m)</t>
+          <t>O484463, N6452943 (±5m)</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Jonas Lindebring</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">

--- a/artfynd/A 21960-2024 artfynd.xlsx
+++ b/artfynd/A 21960-2024 artfynd.xlsx
@@ -1986,7 +1986,7 @@
         <v>121264390</v>
       </c>
       <c r="B14" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         <v>121264388</v>
       </c>
       <c r="B15" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 21960-2024 artfynd.xlsx
+++ b/artfynd/A 21960-2024 artfynd.xlsx
@@ -1983,10 +1983,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121264390</v>
+        <v>121264388</v>
       </c>
       <c r="B14" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2019,17 +2019,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hällemon NO 600 m, Ög</t>
+          <t>Hällemon NO 700 m, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>484410</v>
+        <v>484461</v>
       </c>
       <c r="R14" t="n">
-        <v>6452856</v>
+        <v>6452943</v>
       </c>
       <c r="S14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>E-Öde-0337</t>
+          <t>E-Öde-0339</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>O484410, N6452852 (±5m)</t>
+          <t>O484463, N6452943 (±5m)</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Jonas Lindebring</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2099,10 +2099,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121264388</v>
+        <v>121264390</v>
       </c>
       <c r="B15" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2135,17 +2135,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hällemon NO 700 m, Ög</t>
+          <t>Hällemon NO 600 m, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>484461</v>
+        <v>484410</v>
       </c>
       <c r="R15" t="n">
-        <v>6452943</v>
+        <v>6452856</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>E-Öde-0339</t>
+          <t>E-Öde-0337</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>O484463, N6452943 (±5m)</t>
+          <t>O484410, N6452852 (±5m)</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jonas Lindebring</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">

--- a/artfynd/A 21960-2024 artfynd.xlsx
+++ b/artfynd/A 21960-2024 artfynd.xlsx
@@ -1983,7 +1983,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121264388</v>
+        <v>121264390</v>
       </c>
       <c r="B14" t="n">
         <v>98105</v>
@@ -2019,17 +2019,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hällemon NO 700 m, Ög</t>
+          <t>Hällemon NO 600 m, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>484461</v>
+        <v>484410</v>
       </c>
       <c r="R14" t="n">
-        <v>6452943</v>
+        <v>6452856</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>E-Öde-0339</t>
+          <t>E-Öde-0337</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>O484463, N6452943 (±5m)</t>
+          <t>O484410, N6452852 (±5m)</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jonas Lindebring</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2099,7 +2099,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121264390</v>
+        <v>121264388</v>
       </c>
       <c r="B15" t="n">
         <v>98105</v>
@@ -2135,17 +2135,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hällemon NO 600 m, Ög</t>
+          <t>Hällemon NO 700 m, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>484410</v>
+        <v>484461</v>
       </c>
       <c r="R15" t="n">
-        <v>6452856</v>
+        <v>6452943</v>
       </c>
       <c r="S15" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>E-Öde-0337</t>
+          <t>E-Öde-0339</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>O484410, N6452852 (±5m)</t>
+          <t>O484463, N6452943 (±5m)</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Jonas Lindebring</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">

--- a/artfynd/A 21960-2024 artfynd.xlsx
+++ b/artfynd/A 21960-2024 artfynd.xlsx
@@ -1983,7 +1983,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121264390</v>
+        <v>121264388</v>
       </c>
       <c r="B14" t="n">
         <v>98105</v>
@@ -2019,17 +2019,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hällemon NO 600 m, Ög</t>
+          <t>Hällemon NO 700 m, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>484410</v>
+        <v>484461</v>
       </c>
       <c r="R14" t="n">
-        <v>6452856</v>
+        <v>6452943</v>
       </c>
       <c r="S14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>E-Öde-0337</t>
+          <t>E-Öde-0339</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>O484410, N6452852 (±5m)</t>
+          <t>O484463, N6452943 (±5m)</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Jonas Lindebring</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2099,7 +2099,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121264388</v>
+        <v>121264390</v>
       </c>
       <c r="B15" t="n">
         <v>98105</v>
@@ -2135,17 +2135,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hällemon NO 700 m, Ög</t>
+          <t>Hällemon NO 600 m, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>484461</v>
+        <v>484410</v>
       </c>
       <c r="R15" t="n">
-        <v>6452943</v>
+        <v>6452856</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>E-Öde-0339</t>
+          <t>E-Öde-0337</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>O484463, N6452943 (±5m)</t>
+          <t>O484410, N6452852 (±5m)</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jonas Lindebring</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
